--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomos\Desktop\base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\Git\game\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE571EF-732D-4921-9646-74BA05CA005B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBF60FB-421F-40B9-867F-EE4173B535F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="255" windowWidth="18105" windowHeight="15225" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -363,10 +354,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>フィリップス</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ヤマオカ</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -487,6 +474,10 @@
   </si>
   <si>
     <t>T.スコット</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Phillips</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -870,17 +861,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C402B4-0E60-4338-B3CD-2DB7A1A076E1}">
   <dimension ref="B2:N100"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
@@ -912,7 +903,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
@@ -926,26 +917,26 @@
         <v>8</v>
       </c>
       <c r="F5" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" s="3">
         <v>4</v>
       </c>
       <c r="H5" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I5" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J5" s="3">
         <v>9</v>
       </c>
       <c r="K5">
         <f>SUM(D5:I5)</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
@@ -978,7 +969,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
@@ -1011,7 +1002,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
@@ -1044,7 +1035,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="3" t="s">
         <v>14</v>
       </c>
@@ -1077,7 +1068,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="3" t="s">
         <v>15</v>
       </c>
@@ -1097,20 +1088,20 @@
         <v>3</v>
       </c>
       <c r="H10" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I10" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J10" s="3">
         <v>5</v>
       </c>
       <c r="K10">
         <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1134,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
@@ -1163,20 +1154,20 @@
         <v>3</v>
       </c>
       <c r="H12" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I12" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J12" s="3">
         <v>5</v>
       </c>
       <c r="K12">
         <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="3" t="s">
         <v>19</v>
       </c>
@@ -1209,7 +1200,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="3" t="s">
         <v>20</v>
       </c>
@@ -1242,7 +1233,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="3" t="s">
         <v>21</v>
       </c>
@@ -1275,7 +1266,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="3" t="s">
         <v>45</v>
       </c>
@@ -1308,7 +1299,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="3" t="s">
         <v>46</v>
       </c>
@@ -1341,7 +1332,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="3" t="s">
         <v>47</v>
       </c>
@@ -1374,7 +1365,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="3" t="s">
         <v>48</v>
       </c>
@@ -1407,7 +1398,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="3" t="s">
         <v>49</v>
       </c>
@@ -1440,7 +1431,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="3" t="s">
         <v>55</v>
       </c>
@@ -1473,7 +1464,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="3" t="s">
         <v>61</v>
       </c>
@@ -1506,7 +1497,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="3" t="s">
         <v>59</v>
       </c>
@@ -1539,7 +1530,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="3" t="s">
         <v>62</v>
       </c>
@@ -1556,23 +1547,23 @@
         <v>5</v>
       </c>
       <c r="G24" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H24" s="3">
         <v>2</v>
       </c>
       <c r="I24" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J24" s="3">
         <v>5</v>
       </c>
       <c r="K24">
         <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="3" t="s">
         <v>63</v>
       </c>
@@ -1605,9 +1596,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:11" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>44</v>
@@ -1638,7 +1629,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="3" t="s">
         <v>78</v>
       </c>
@@ -1671,7 +1662,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="3" t="s">
         <v>80</v>
       </c>
@@ -1704,7 +1695,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="3" t="s">
         <v>81</v>
       </c>
@@ -1737,7 +1728,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="3" t="s">
         <v>82</v>
       </c>
@@ -1770,7 +1761,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="3" t="s">
         <v>74</v>
       </c>
@@ -1803,7 +1794,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="3" t="s">
         <v>85</v>
       </c>
@@ -1836,7 +1827,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="3" t="s">
         <v>79</v>
       </c>
@@ -1869,7 +1860,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="3" t="s">
         <v>86</v>
       </c>
@@ -1902,7 +1893,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="3" t="s">
         <v>87</v>
       </c>
@@ -1935,9 +1926,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>44</v>
@@ -1968,9 +1959,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>44</v>
@@ -2001,12 +1992,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="D38" s="3">
         <v>4</v>
@@ -2034,9 +2025,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>44</v>
@@ -2067,9 +2058,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>52</v>
@@ -2100,9 +2091,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>52</v>
@@ -2120,7 +2111,7 @@
         <v>3</v>
       </c>
       <c r="H41" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I41" s="3">
         <v>6</v>
@@ -2130,12 +2121,12 @@
       </c>
       <c r="K41">
         <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>52</v>
@@ -2166,9 +2157,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>44</v>
@@ -2199,9 +2190,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>52</v>
@@ -2232,13 +2223,13 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J45" s="3"/>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="2" t="s">
         <v>1</v>
       </c>
@@ -2279,7 +2270,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="3" t="s">
         <v>32</v>
       </c>
@@ -2321,7 +2312,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="3" t="s">
         <v>33</v>
       </c>
@@ -2363,7 +2354,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="3" t="s">
         <v>34</v>
       </c>
@@ -2405,7 +2396,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="3" t="s">
         <v>35</v>
       </c>
@@ -2447,7 +2438,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="3" t="s">
         <v>36</v>
       </c>
@@ -2489,7 +2480,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="3" t="s">
         <v>37</v>
       </c>
@@ -2531,7 +2522,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="3" t="s">
         <v>38</v>
       </c>
@@ -2573,7 +2564,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="3" t="s">
         <v>39</v>
       </c>
@@ -2615,7 +2606,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="3" t="s">
         <v>40</v>
       </c>
@@ -2657,7 +2648,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="3" t="s">
         <v>41</v>
       </c>
@@ -2699,7 +2690,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="3" t="s">
         <v>42</v>
       </c>
@@ -2741,7 +2732,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="3" t="s">
         <v>43</v>
       </c>
@@ -2783,7 +2774,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="3" t="s">
         <v>53</v>
       </c>
@@ -2825,7 +2816,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="3" t="s">
         <v>54</v>
       </c>
@@ -2867,7 +2858,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="3" t="s">
         <v>57</v>
       </c>
@@ -2909,7 +2900,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="3" t="s">
         <v>60</v>
       </c>
@@ -2951,7 +2942,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="3" t="s">
         <v>61</v>
       </c>
@@ -2993,7 +2984,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="3" t="s">
         <v>64</v>
       </c>
@@ -3035,7 +3026,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="3" t="s">
         <v>71</v>
       </c>
@@ -3077,7 +3068,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="3" t="s">
         <v>72</v>
       </c>
@@ -3119,7 +3110,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="3" t="s">
         <v>73</v>
       </c>
@@ -3161,7 +3152,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="3" t="s">
         <v>75</v>
       </c>
@@ -3203,7 +3194,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="70" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="3" t="s">
         <v>76</v>
       </c>
@@ -3245,9 +3236,9 @@
         <v>172</v>
       </c>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="71" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="3" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>44</v>
@@ -3256,7 +3247,7 @@
         <v>158</v>
       </c>
       <c r="E71" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F71" s="3">
         <v>3</v>
@@ -3265,13 +3256,13 @@
         <v>3</v>
       </c>
       <c r="H71" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I71" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J71" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K71" s="3">
         <v>5</v>
@@ -3284,12 +3275,12 @@
       </c>
       <c r="N71">
         <f t="shared" si="1"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>44</v>
@@ -3329,9 +3320,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>44</v>
@@ -3371,9 +3362,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="74" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>44</v>
@@ -3413,9 +3404,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>44</v>
@@ -3455,9 +3446,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>52</v>
@@ -3497,9 +3488,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>44</v>
@@ -3520,7 +3511,7 @@
         <v>4</v>
       </c>
       <c r="I77" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J77" s="3">
         <v>6</v>
@@ -3536,12 +3527,12 @@
       </c>
       <c r="N77">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="78" spans="2:14" x14ac:dyDescent="0.4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="78" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>44</v>
@@ -3562,7 +3553,7 @@
         <v>4</v>
       </c>
       <c r="I78" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J78" s="3">
         <v>7</v>
@@ -3578,12 +3569,12 @@
       </c>
       <c r="N78">
         <f t="shared" si="1"/>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>52</v>
@@ -3623,9 +3614,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>44</v>
@@ -3665,9 +3656,9 @@
         <v>161</v>
       </c>
     </row>
-    <row r="81" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="81" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>52</v>
@@ -3707,9 +3698,9 @@
         <v>159</v>
       </c>
     </row>
-    <row r="82" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="82" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>44</v>
@@ -3749,9 +3740,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="83" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>52</v>
@@ -3791,9 +3782,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="84" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="84" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>52</v>
@@ -3833,9 +3824,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>44</v>
@@ -3875,9 +3866,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="86" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="86" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>44</v>
@@ -3898,7 +3889,7 @@
         <v>6</v>
       </c>
       <c r="I86" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J86" s="3">
         <v>8</v>
@@ -3914,12 +3905,12 @@
       </c>
       <c r="N86">
         <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="87" spans="2:14" x14ac:dyDescent="0.4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="87" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>44</v>
@@ -3959,9 +3950,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="88" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="88" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>52</v>
@@ -4001,9 +3992,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="89" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>44</v>
@@ -4024,7 +4015,7 @@
         <v>5</v>
       </c>
       <c r="I89" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J89" s="3">
         <v>6</v>
@@ -4040,15 +4031,15 @@
       </c>
       <c r="N89">
         <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="90" spans="2:14" x14ac:dyDescent="0.4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="90" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="91" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="91" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" s="2" t="s">
         <v>1</v>
       </c>
@@ -4074,7 +4065,7 @@
       </c>
       <c r="K91" s="2"/>
     </row>
-    <row r="92" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="92" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" t="s">
         <v>70</v>
       </c>
@@ -4097,7 +4088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" t="s">
         <v>67</v>
       </c>
@@ -4120,7 +4111,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="94" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" t="s">
         <v>68</v>
       </c>
@@ -4143,7 +4134,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="95" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="95" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" t="s">
         <v>69</v>
       </c>
@@ -4166,7 +4157,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="96" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" t="s">
         <v>58</v>
       </c>
@@ -4189,7 +4180,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" t="s">
         <v>61</v>
       </c>
@@ -4212,7 +4203,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" t="s">
         <v>77</v>
       </c>
@@ -4235,7 +4226,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" t="s">
         <v>83</v>
       </c>
@@ -4258,9 +4249,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C100" t="s">
         <v>66</v>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\Git\game\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBF60FB-421F-40B9-867F-EE4173B535F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F2783A-6C8C-4AD5-9575-FD59DFDB2D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
+    <workbookView xWindow="10400" yWindow="3690" windowWidth="29360" windowHeight="18110" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="121">
   <si>
     <t>野手・打者</t>
   </si>
@@ -477,7 +488,15 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Phillips</t>
+    <t>フィリップス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シンプソン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シュリトラー</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -564,9 +583,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -604,7 +623,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -710,7 +729,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -852,7 +871,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -860,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C402B4-0E60-4338-B3CD-2DB7A1A076E1}">
-  <dimension ref="B2:N100"/>
+  <dimension ref="B2:N103"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -917,23 +936,23 @@
         <v>8</v>
       </c>
       <c r="F5" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="3">
         <v>4</v>
       </c>
       <c r="H5" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="3">
         <v>8</v>
       </c>
       <c r="J5" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <f>SUM(D5:I5)</f>
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -995,7 +1014,7 @@
         <v>6</v>
       </c>
       <c r="J7" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
@@ -1010,7 +1029,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" s="3">
         <v>9</v>
@@ -1032,7 +1051,7 @@
       </c>
       <c r="K8">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1061,7 +1080,7 @@
         <v>2</v>
       </c>
       <c r="J9" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <f t="shared" si="0"/>
@@ -1094,7 +1113,7 @@
         <v>6</v>
       </c>
       <c r="J10" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10">
         <f t="shared" si="0"/>
@@ -1154,17 +1173,17 @@
         <v>3</v>
       </c>
       <c r="H12" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I12" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J12" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K12">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1187,7 +1206,7 @@
         <v>3</v>
       </c>
       <c r="H13" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I13" s="3">
         <v>5</v>
@@ -1197,7 +1216,7 @@
       </c>
       <c r="K13">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1211,26 +1230,26 @@
         <v>10</v>
       </c>
       <c r="E14" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14" s="3">
         <v>3</v>
       </c>
       <c r="H14" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I14" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1253,17 +1272,17 @@
         <v>3</v>
       </c>
       <c r="H15" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" s="3">
         <v>30</v>
       </c>
       <c r="K15">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1292,7 +1311,7 @@
         <v>5</v>
       </c>
       <c r="J16" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16">
         <f t="shared" si="0"/>
@@ -1316,20 +1335,20 @@
         <v>6</v>
       </c>
       <c r="G17" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H17" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I17" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J17" s="3">
         <v>5</v>
       </c>
       <c r="K17">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1358,7 +1377,7 @@
         <v>7</v>
       </c>
       <c r="J18" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K18">
         <f t="shared" si="0"/>
@@ -1391,7 +1410,7 @@
         <v>3</v>
       </c>
       <c r="J19" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K19">
         <f t="shared" si="0"/>
@@ -1457,7 +1476,7 @@
         <v>6</v>
       </c>
       <c r="J21" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K21">
         <f t="shared" si="0"/>
@@ -1490,7 +1509,7 @@
         <v>6</v>
       </c>
       <c r="J22" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22">
         <f t="shared" si="0"/>
@@ -1523,7 +1542,7 @@
         <v>7</v>
       </c>
       <c r="J23" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <f t="shared" si="0"/>
@@ -1589,7 +1608,7 @@
         <v>7</v>
       </c>
       <c r="J25" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K25">
         <f t="shared" si="0"/>
@@ -1622,7 +1641,7 @@
         <v>6</v>
       </c>
       <c r="J26" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <f t="shared" si="0"/>
@@ -1688,7 +1707,7 @@
         <v>7</v>
       </c>
       <c r="J28" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K28">
         <f t="shared" si="0"/>
@@ -1721,7 +1740,7 @@
         <v>2</v>
       </c>
       <c r="J29" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K29">
         <f t="shared" si="0"/>
@@ -1754,7 +1773,7 @@
         <v>6</v>
       </c>
       <c r="J30" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K30">
         <f t="shared" si="0"/>
@@ -1802,10 +1821,10 @@
         <v>52</v>
       </c>
       <c r="D32" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" s="3">
         <v>4</v>
@@ -1820,14 +1839,14 @@
         <v>4</v>
       </c>
       <c r="J32" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K32">
         <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="3" t="s">
         <v>79</v>
       </c>
@@ -1860,7 +1879,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="3" t="s">
         <v>86</v>
       </c>
@@ -1886,14 +1905,14 @@
         <v>6</v>
       </c>
       <c r="J34" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K34">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="3" t="s">
         <v>87</v>
       </c>
@@ -1919,14 +1938,14 @@
         <v>3</v>
       </c>
       <c r="J35" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K35">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="3" t="s">
         <v>90</v>
       </c>
@@ -1952,14 +1971,14 @@
         <v>8</v>
       </c>
       <c r="J36" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K36">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="3" t="s">
         <v>91</v>
       </c>
@@ -1985,14 +2004,14 @@
         <v>3</v>
       </c>
       <c r="J37" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K37">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="3" t="s">
         <v>101</v>
       </c>
@@ -2025,7 +2044,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="3" t="s">
         <v>103</v>
       </c>
@@ -2058,7 +2077,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="3" t="s">
         <v>107</v>
       </c>
@@ -2091,7 +2110,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="3" t="s">
         <v>110</v>
       </c>
@@ -2117,14 +2136,14 @@
         <v>6</v>
       </c>
       <c r="J41" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K41">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="3" t="s">
         <v>111</v>
       </c>
@@ -2157,7 +2176,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="3" t="s">
         <v>113</v>
       </c>
@@ -2183,14 +2202,14 @@
         <v>6</v>
       </c>
       <c r="J43" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K43">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="3" t="s">
         <v>114</v>
       </c>
@@ -2210,2065 +2229,2151 @@
         <v>4</v>
       </c>
       <c r="H44" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I44" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J44" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K44">
         <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" s="3">
+        <v>1</v>
+      </c>
+      <c r="E45" s="3">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
+        <v>9</v>
+      </c>
+      <c r="G45" s="3">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
+        <v>4</v>
+      </c>
+      <c r="K45">
+        <f>SUM(D45:J45)</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J45" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="2" t="s">
+      <c r="J47" s="3"/>
+    </row>
+    <row r="49" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E49" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F49" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G49" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H47" s="2" t="s">
+      <c r="H49" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I47" s="2" t="s">
+      <c r="I49" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J47" s="2" t="s">
+      <c r="J49" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L47" s="2" t="s">
+      <c r="K49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L49" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N47" s="2" t="s">
+      <c r="M49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N49" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" s="3">
-        <v>165</v>
-      </c>
-      <c r="E48" s="3">
-        <v>9</v>
-      </c>
-      <c r="F48" s="3">
-        <v>5</v>
-      </c>
-      <c r="G48" s="3">
-        <v>8</v>
-      </c>
-      <c r="H48" s="3">
-        <v>8</v>
-      </c>
-      <c r="I48" s="3">
-        <v>6</v>
-      </c>
-      <c r="J48" s="3">
-        <v>8</v>
-      </c>
-      <c r="K48" s="3">
-        <v>7</v>
-      </c>
-      <c r="L48" s="3">
-        <v>6</v>
-      </c>
-      <c r="M48" s="3">
-        <v>9</v>
-      </c>
-      <c r="N48">
-        <f>SUM(E48:L48)</f>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D49" s="3">
-        <v>157</v>
-      </c>
-      <c r="E49" s="3">
-        <v>8</v>
-      </c>
-      <c r="F49" s="3">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3">
-        <v>7</v>
-      </c>
-      <c r="H49" s="3">
-        <v>7</v>
-      </c>
-      <c r="I49" s="3">
-        <v>9</v>
-      </c>
-      <c r="J49" s="3">
-        <v>7</v>
-      </c>
-      <c r="K49" s="3">
-        <v>6</v>
-      </c>
-      <c r="L49" s="3">
-        <v>7</v>
-      </c>
-      <c r="M49" s="3">
-        <v>8</v>
-      </c>
-      <c r="N49">
-        <f t="shared" ref="N49:N89" si="1">SUM(E49:L49)</f>
-        <v>54</v>
       </c>
     </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D50" s="3">
+        <v>165</v>
+      </c>
+      <c r="E50" s="3">
+        <v>9</v>
+      </c>
+      <c r="F50" s="3">
+        <v>5</v>
+      </c>
+      <c r="G50" s="3">
+        <v>8</v>
+      </c>
+      <c r="H50" s="3">
+        <v>8</v>
+      </c>
+      <c r="I50" s="3">
+        <v>7</v>
+      </c>
+      <c r="J50" s="3">
+        <v>9</v>
+      </c>
+      <c r="K50" s="3">
+        <v>7</v>
+      </c>
+      <c r="L50" s="3">
+        <v>6</v>
+      </c>
+      <c r="M50" s="3">
+        <v>10</v>
+      </c>
+      <c r="N50">
+        <f>SUM(E50:L50)</f>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="3">
+        <v>157</v>
+      </c>
+      <c r="E51" s="3">
+        <v>9</v>
+      </c>
+      <c r="F51" s="3">
+        <v>4</v>
+      </c>
+      <c r="G51" s="3">
+        <v>7</v>
+      </c>
+      <c r="H51" s="3">
+        <v>7</v>
+      </c>
+      <c r="I51" s="3">
+        <v>9</v>
+      </c>
+      <c r="J51" s="3">
+        <v>7</v>
+      </c>
+      <c r="K51" s="3">
+        <v>7</v>
+      </c>
+      <c r="L51" s="3">
+        <v>7</v>
+      </c>
+      <c r="M51" s="3">
+        <v>10</v>
+      </c>
+      <c r="N51">
+        <f t="shared" ref="N51:N92" si="1">SUM(E51:L51)</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="3">
         <v>155</v>
       </c>
-      <c r="E50" s="3">
-        <v>5</v>
-      </c>
-      <c r="F50" s="3">
-        <v>2</v>
-      </c>
-      <c r="G50" s="3">
+      <c r="E52" s="3">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3">
+        <v>2</v>
+      </c>
+      <c r="G52" s="3">
         <v>10</v>
       </c>
-      <c r="H50" s="3">
-        <v>6</v>
-      </c>
-      <c r="I50" s="3">
-        <v>6</v>
-      </c>
-      <c r="J50" s="3">
-        <v>6</v>
-      </c>
-      <c r="K50" s="3">
-        <v>5</v>
-      </c>
-      <c r="L50" s="3">
-        <v>7</v>
-      </c>
-      <c r="M50" s="3">
-        <v>6</v>
-      </c>
-      <c r="N50">
+      <c r="H52" s="3">
+        <v>6</v>
+      </c>
+      <c r="I52" s="3">
+        <v>6</v>
+      </c>
+      <c r="J52" s="3">
+        <v>6</v>
+      </c>
+      <c r="K52" s="3">
+        <v>5</v>
+      </c>
+      <c r="L52" s="3">
+        <v>7</v>
+      </c>
+      <c r="M52" s="3">
+        <v>5</v>
+      </c>
+      <c r="N52">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="3" t="s">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D53" s="3">
         <v>148</v>
       </c>
-      <c r="E51" s="3">
-        <v>4</v>
-      </c>
-      <c r="F51" s="3">
+      <c r="E53" s="3">
+        <v>4</v>
+      </c>
+      <c r="F53" s="3">
         <v>10</v>
       </c>
-      <c r="G51" s="3">
-        <v>6</v>
-      </c>
-      <c r="H51" s="3">
-        <v>4</v>
-      </c>
-      <c r="I51" s="3">
-        <v>8</v>
-      </c>
-      <c r="J51" s="3">
-        <v>5</v>
-      </c>
-      <c r="K51" s="3">
-        <v>4</v>
-      </c>
-      <c r="L51" s="3">
-        <v>5</v>
-      </c>
-      <c r="M51" s="3">
-        <v>6</v>
-      </c>
-      <c r="N51">
+      <c r="G53" s="3">
+        <v>6</v>
+      </c>
+      <c r="H53" s="3">
+        <v>4</v>
+      </c>
+      <c r="I53" s="3">
+        <v>8</v>
+      </c>
+      <c r="J53" s="3">
+        <v>5</v>
+      </c>
+      <c r="K53" s="3">
+        <v>4</v>
+      </c>
+      <c r="L53" s="3">
+        <v>5</v>
+      </c>
+      <c r="M53" s="3">
+        <v>5</v>
+      </c>
+      <c r="N53">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="3" t="s">
+    <row r="54" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D54" s="3">
         <v>220</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E54" s="3">
         <v>1</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F54" s="3">
         <v>1</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G54" s="3">
         <v>9</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H54" s="3">
         <v>1</v>
       </c>
-      <c r="I52" s="3">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3">
-        <v>6</v>
-      </c>
-      <c r="K52" s="3">
-        <v>4</v>
-      </c>
-      <c r="L52" s="3">
-        <v>6</v>
-      </c>
-      <c r="M52" s="3">
-        <v>5</v>
-      </c>
-      <c r="N52">
+      <c r="I54" s="3">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3">
+        <v>6</v>
+      </c>
+      <c r="K54" s="3">
+        <v>4</v>
+      </c>
+      <c r="L54" s="3">
+        <v>6</v>
+      </c>
+      <c r="M54" s="3">
+        <v>4</v>
+      </c>
+      <c r="N54">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="3" t="s">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D55" s="3">
         <v>100</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E55" s="3">
         <v>9</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F55" s="3">
         <v>9</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G55" s="3">
         <v>9</v>
       </c>
-      <c r="H53" s="3">
+      <c r="H55" s="3">
         <v>9</v>
       </c>
-      <c r="I53" s="3">
+      <c r="I55" s="3">
         <v>9</v>
       </c>
-      <c r="J53" s="3">
-        <v>6</v>
-      </c>
-      <c r="K53" s="3">
-        <v>8</v>
-      </c>
-      <c r="L53" s="3">
-        <v>4</v>
-      </c>
-      <c r="M53" s="3">
-        <v>5</v>
-      </c>
-      <c r="N53">
+      <c r="J55" s="3">
+        <v>6</v>
+      </c>
+      <c r="K55" s="3">
+        <v>8</v>
+      </c>
+      <c r="L55" s="3">
+        <v>4</v>
+      </c>
+      <c r="M55" s="3">
+        <v>4</v>
+      </c>
+      <c r="N55">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="3" t="s">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D56" s="3">
         <v>149</v>
       </c>
-      <c r="E54" s="3">
-        <v>3</v>
-      </c>
-      <c r="F54" s="3">
-        <v>6</v>
-      </c>
-      <c r="G54" s="3">
-        <v>5</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="E56" s="3">
+        <v>3</v>
+      </c>
+      <c r="F56" s="3">
+        <v>6</v>
+      </c>
+      <c r="G56" s="3">
+        <v>5</v>
+      </c>
+      <c r="H56" s="3">
         <v>10</v>
       </c>
-      <c r="I54" s="3">
-        <v>5</v>
-      </c>
-      <c r="J54" s="3">
-        <v>8</v>
-      </c>
-      <c r="K54" s="3">
-        <v>5</v>
-      </c>
-      <c r="L54" s="3">
-        <v>6</v>
-      </c>
-      <c r="M54" s="3">
-        <v>6</v>
-      </c>
-      <c r="N54">
+      <c r="I56" s="3">
+        <v>5</v>
+      </c>
+      <c r="J56" s="3">
+        <v>8</v>
+      </c>
+      <c r="K56" s="3">
+        <v>5</v>
+      </c>
+      <c r="L56" s="3">
+        <v>6</v>
+      </c>
+      <c r="M56" s="3">
+        <v>5</v>
+      </c>
+      <c r="N56">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
     </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="3" t="s">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D57" s="3">
         <v>158</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E57" s="3">
         <v>9</v>
       </c>
-      <c r="F55" s="3">
-        <v>8</v>
-      </c>
-      <c r="G55" s="3">
-        <v>6</v>
-      </c>
-      <c r="H55" s="3">
-        <v>5</v>
-      </c>
-      <c r="I55" s="3">
-        <v>7</v>
-      </c>
-      <c r="J55" s="3">
-        <v>4</v>
-      </c>
-      <c r="K55" s="3">
-        <v>5</v>
-      </c>
-      <c r="L55" s="3">
-        <v>5</v>
-      </c>
-      <c r="M55" s="3">
-        <v>6</v>
-      </c>
-      <c r="N55">
+      <c r="F57" s="3">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3">
+        <v>6</v>
+      </c>
+      <c r="H57" s="3">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3">
+        <v>7</v>
+      </c>
+      <c r="J57" s="3">
+        <v>4</v>
+      </c>
+      <c r="K57" s="3">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
+        <v>5</v>
+      </c>
+      <c r="M57" s="3">
+        <v>5</v>
+      </c>
+      <c r="N57">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="3" t="s">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D58" s="3">
         <v>172</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E58" s="3">
         <v>17</v>
       </c>
-      <c r="F56" s="3">
+      <c r="F58" s="3">
         <v>16</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G58" s="3">
         <v>24</v>
       </c>
-      <c r="H56" s="3">
+      <c r="H58" s="3">
         <v>17</v>
       </c>
-      <c r="I56" s="3">
+      <c r="I58" s="3">
         <v>25</v>
       </c>
-      <c r="J56" s="3">
+      <c r="J58" s="3">
         <v>32</v>
       </c>
-      <c r="K56" s="3">
-        <v>7</v>
-      </c>
-      <c r="L56" s="3">
+      <c r="K58" s="3">
+        <v>7</v>
+      </c>
+      <c r="L58" s="3">
         <v>16</v>
       </c>
-      <c r="M56" s="3">
+      <c r="M58" s="3">
         <v>30</v>
       </c>
-      <c r="N56">
+      <c r="N58">
         <f t="shared" si="1"/>
         <v>154</v>
       </c>
     </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="3" t="s">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D59" s="3">
         <v>171</v>
       </c>
-      <c r="E57" s="3">
-        <v>8</v>
-      </c>
-      <c r="F57" s="3">
-        <v>6</v>
-      </c>
-      <c r="G57" s="3">
-        <v>8</v>
-      </c>
-      <c r="H57" s="3">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3">
-        <v>8</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="E59" s="3">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3">
+        <v>6</v>
+      </c>
+      <c r="G59" s="3">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
         <v>14</v>
       </c>
-      <c r="K57" s="3">
-        <v>6</v>
-      </c>
-      <c r="L57" s="3">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3">
-        <v>4</v>
-      </c>
-      <c r="N57">
+      <c r="K59" s="3">
+        <v>6</v>
+      </c>
+      <c r="L59" s="3">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
+        <v>4</v>
+      </c>
+      <c r="N59">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="3" t="s">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D60" s="3">
         <v>143</v>
       </c>
-      <c r="E58" s="3">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3">
-        <v>4</v>
-      </c>
-      <c r="G58" s="3">
-        <v>5</v>
-      </c>
-      <c r="H58" s="3">
-        <v>5</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="E60" s="3">
+        <v>4</v>
+      </c>
+      <c r="F60" s="3">
+        <v>4</v>
+      </c>
+      <c r="G60" s="3">
+        <v>5</v>
+      </c>
+      <c r="H60" s="3">
+        <v>5</v>
+      </c>
+      <c r="I60" s="3">
         <v>10</v>
       </c>
-      <c r="J58" s="3">
-        <v>7</v>
-      </c>
-      <c r="K58" s="3">
-        <v>8</v>
-      </c>
-      <c r="L58" s="3">
-        <v>6</v>
-      </c>
-      <c r="M58" s="3">
-        <v>6</v>
-      </c>
-      <c r="N58">
+      <c r="J60" s="3">
+        <v>7</v>
+      </c>
+      <c r="K60" s="3">
+        <v>8</v>
+      </c>
+      <c r="L60" s="3">
+        <v>6</v>
+      </c>
+      <c r="M60" s="3">
+        <v>5</v>
+      </c>
+      <c r="N60">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="3" t="s">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D61" s="3">
         <v>169</v>
       </c>
-      <c r="E59" s="3">
-        <v>7</v>
-      </c>
-      <c r="F59" s="3">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3">
-        <v>5</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="E61" s="3">
         <v>9</v>
       </c>
-      <c r="I59" s="3">
-        <v>5</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="F61" s="3">
+        <v>5</v>
+      </c>
+      <c r="G61" s="3">
+        <v>6</v>
+      </c>
+      <c r="H61" s="3">
         <v>9</v>
       </c>
-      <c r="K59" s="3">
-        <v>4</v>
-      </c>
-      <c r="L59" s="3">
-        <v>7</v>
-      </c>
-      <c r="M59" s="3">
-        <v>8</v>
-      </c>
-      <c r="N59">
+      <c r="I61" s="3">
+        <v>8</v>
+      </c>
+      <c r="J61" s="3">
+        <v>10</v>
+      </c>
+      <c r="K61" s="3">
+        <v>5</v>
+      </c>
+      <c r="L61" s="3">
+        <v>7</v>
+      </c>
+      <c r="M61" s="3">
+        <v>10</v>
+      </c>
+      <c r="N61">
         <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D62" s="3">
         <v>156</v>
       </c>
-      <c r="E60" s="3">
-        <v>2</v>
-      </c>
-      <c r="F60" s="3">
+      <c r="E62" s="3">
+        <v>2</v>
+      </c>
+      <c r="F62" s="3">
         <v>10</v>
       </c>
-      <c r="G60" s="3">
-        <v>2</v>
-      </c>
-      <c r="H60" s="3">
-        <v>2</v>
-      </c>
-      <c r="I60" s="3">
-        <v>5</v>
-      </c>
-      <c r="J60" s="3">
-        <v>2</v>
-      </c>
-      <c r="K60" s="3">
-        <v>5</v>
-      </c>
-      <c r="L60" s="3">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="G62" s="3">
+        <v>2</v>
+      </c>
+      <c r="H62" s="3">
+        <v>2</v>
+      </c>
+      <c r="I62" s="3">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3">
+        <v>2</v>
+      </c>
+      <c r="K62" s="3">
+        <v>5</v>
+      </c>
+      <c r="L62" s="3">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>1</v>
       </c>
-      <c r="N60">
+      <c r="N62">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="3" t="s">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D63" s="3">
         <v>158</v>
       </c>
-      <c r="E61" s="3">
-        <v>2</v>
-      </c>
-      <c r="F61" s="3">
+      <c r="E63" s="3">
+        <v>2</v>
+      </c>
+      <c r="F63" s="3">
         <v>1</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G63" s="3">
         <v>9</v>
       </c>
-      <c r="H61" s="3">
-        <v>7</v>
-      </c>
-      <c r="I61" s="3">
-        <v>3</v>
-      </c>
-      <c r="J61" s="3">
+      <c r="H63" s="3">
+        <v>7</v>
+      </c>
+      <c r="I63" s="3">
+        <v>3</v>
+      </c>
+      <c r="J63" s="3">
         <v>9</v>
       </c>
-      <c r="K61" s="3">
-        <v>3</v>
-      </c>
-      <c r="L61" s="3">
-        <v>3</v>
-      </c>
-      <c r="M61" s="3">
-        <v>3</v>
-      </c>
-      <c r="N61">
+      <c r="K63" s="3">
+        <v>3</v>
+      </c>
+      <c r="L63" s="3">
+        <v>3</v>
+      </c>
+      <c r="M63" s="3">
+        <v>2</v>
+      </c>
+      <c r="N63">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
     </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="3" t="s">
+    <row r="64" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D64" s="3">
         <v>165</v>
       </c>
-      <c r="E62" s="3">
-        <v>5</v>
-      </c>
-      <c r="F62" s="3">
-        <v>2</v>
-      </c>
-      <c r="G62" s="3">
-        <v>6</v>
-      </c>
-      <c r="H62" s="3">
-        <v>4</v>
-      </c>
-      <c r="I62" s="3">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3">
-        <v>7</v>
-      </c>
-      <c r="K62" s="3">
-        <v>4</v>
-      </c>
-      <c r="L62" s="3">
-        <v>5</v>
-      </c>
-      <c r="M62" s="3">
-        <v>6</v>
-      </c>
-      <c r="N62">
+      <c r="E64" s="3">
+        <v>7</v>
+      </c>
+      <c r="F64" s="3">
+        <v>3</v>
+      </c>
+      <c r="G64" s="3">
+        <v>8</v>
+      </c>
+      <c r="H64" s="3">
+        <v>7</v>
+      </c>
+      <c r="I64" s="3">
+        <v>4</v>
+      </c>
+      <c r="J64" s="3">
+        <v>8</v>
+      </c>
+      <c r="K64" s="3">
+        <v>4</v>
+      </c>
+      <c r="L64" s="3">
+        <v>5</v>
+      </c>
+      <c r="M64" s="3">
+        <v>5</v>
+      </c>
+      <c r="N64">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D65" s="3">
+        <v>150</v>
+      </c>
+      <c r="E65" s="3">
+        <v>2</v>
+      </c>
+      <c r="F65" s="3">
+        <v>5</v>
+      </c>
+      <c r="G65" s="3">
+        <v>5</v>
+      </c>
+      <c r="H65" s="3">
+        <v>5</v>
+      </c>
+      <c r="I65" s="3">
+        <v>5</v>
+      </c>
+      <c r="J65" s="3">
+        <v>5</v>
+      </c>
+      <c r="K65" s="3">
+        <v>5</v>
+      </c>
+      <c r="L65" s="3">
+        <v>3</v>
+      </c>
+      <c r="M65" s="3">
+        <v>2</v>
+      </c>
+      <c r="N65">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" s="3">
+        <v>125</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2</v>
+      </c>
+      <c r="F66" s="3">
+        <v>2</v>
+      </c>
+      <c r="G66" s="3">
+        <v>3</v>
+      </c>
+      <c r="H66" s="3">
+        <v>1</v>
+      </c>
+      <c r="I66" s="3">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3">
+        <v>3</v>
+      </c>
+      <c r="K66" s="3">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3">
+        <v>2</v>
+      </c>
+      <c r="N66">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" s="3">
+        <v>159</v>
+      </c>
+      <c r="E67" s="3">
+        <v>7</v>
+      </c>
+      <c r="F67" s="3">
+        <v>3</v>
+      </c>
+      <c r="G67" s="3">
+        <v>5</v>
+      </c>
+      <c r="H67" s="3">
+        <v>5</v>
+      </c>
+      <c r="I67" s="3">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3">
+        <v>9</v>
+      </c>
+      <c r="K67" s="3">
+        <v>3</v>
+      </c>
+      <c r="L67" s="3">
+        <v>6</v>
+      </c>
+      <c r="M67" s="3">
+        <v>4</v>
+      </c>
+      <c r="N67">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D68" s="3">
+        <v>164</v>
+      </c>
+      <c r="E68" s="3">
+        <v>7</v>
+      </c>
+      <c r="F68" s="3">
+        <v>9</v>
+      </c>
+      <c r="G68" s="3">
+        <v>9</v>
+      </c>
+      <c r="H68" s="3">
+        <v>8</v>
+      </c>
+      <c r="I68" s="3">
+        <v>8</v>
+      </c>
+      <c r="J68" s="3">
+        <v>8</v>
+      </c>
+      <c r="K68" s="3">
+        <v>6</v>
+      </c>
+      <c r="L68" s="3">
+        <v>7</v>
+      </c>
+      <c r="M68" s="3">
+        <v>10</v>
+      </c>
+      <c r="N68">
+        <f t="shared" si="1"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D69" s="3">
+        <v>157</v>
+      </c>
+      <c r="E69" s="3">
+        <v>4</v>
+      </c>
+      <c r="F69" s="3">
+        <v>7</v>
+      </c>
+      <c r="G69" s="3">
+        <v>5</v>
+      </c>
+      <c r="H69" s="3">
+        <v>5</v>
+      </c>
+      <c r="I69" s="3">
+        <v>6</v>
+      </c>
+      <c r="J69" s="3">
+        <v>6</v>
+      </c>
+      <c r="K69" s="3">
+        <v>5</v>
+      </c>
+      <c r="L69" s="3">
+        <v>4</v>
+      </c>
+      <c r="M69" s="3">
+        <v>3</v>
+      </c>
+      <c r="N69">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D70" s="3">
+        <v>155</v>
+      </c>
+      <c r="E70" s="3">
+        <v>4</v>
+      </c>
+      <c r="F70" s="3">
+        <v>3</v>
+      </c>
+      <c r="G70" s="3">
+        <v>8</v>
+      </c>
+      <c r="H70" s="3">
+        <v>3</v>
+      </c>
+      <c r="I70" s="3">
+        <v>9</v>
+      </c>
+      <c r="J70" s="3">
+        <v>5</v>
+      </c>
+      <c r="K70" s="3">
+        <v>8</v>
+      </c>
+      <c r="L70" s="3">
+        <v>6</v>
+      </c>
+      <c r="M70" s="3">
+        <v>5</v>
+      </c>
+      <c r="N70">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D71" s="3">
+        <v>175</v>
+      </c>
+      <c r="E71" s="3">
+        <v>18</v>
+      </c>
+      <c r="F71" s="3">
+        <v>17</v>
+      </c>
+      <c r="G71" s="3">
+        <v>27</v>
+      </c>
+      <c r="H71" s="3">
+        <v>17</v>
+      </c>
+      <c r="I71" s="3">
+        <v>27</v>
+      </c>
+      <c r="J71" s="3">
+        <v>33</v>
+      </c>
+      <c r="K71" s="3">
+        <v>7</v>
+      </c>
+      <c r="L71" s="3">
+        <v>16</v>
+      </c>
+      <c r="M71" s="3">
+        <v>32</v>
+      </c>
+      <c r="N71">
+        <f t="shared" si="1"/>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D72" s="3">
+        <v>155</v>
+      </c>
+      <c r="E72" s="3">
+        <v>22</v>
+      </c>
+      <c r="F72" s="3">
+        <v>20</v>
+      </c>
+      <c r="G72" s="3">
+        <v>29</v>
+      </c>
+      <c r="H72" s="3">
+        <v>18</v>
+      </c>
+      <c r="I72" s="3">
+        <v>29</v>
+      </c>
+      <c r="J72" s="3">
+        <v>32</v>
+      </c>
+      <c r="K72" s="3">
+        <v>7</v>
+      </c>
+      <c r="L72" s="3">
+        <v>15</v>
+      </c>
+      <c r="M72" s="3">
+        <v>32</v>
+      </c>
+      <c r="N72">
+        <f t="shared" si="1"/>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D73" s="3">
+        <v>158</v>
+      </c>
+      <c r="E73" s="3">
+        <v>8</v>
+      </c>
+      <c r="F73" s="3">
+        <v>3</v>
+      </c>
+      <c r="G73" s="3">
+        <v>3</v>
+      </c>
+      <c r="H73" s="3">
+        <v>6</v>
+      </c>
+      <c r="I73" s="3">
+        <v>7</v>
+      </c>
+      <c r="J73" s="3">
+        <v>8</v>
+      </c>
+      <c r="K73" s="3">
+        <v>5</v>
+      </c>
+      <c r="L73" s="3">
+        <v>3</v>
+      </c>
+      <c r="M73" s="3">
+        <v>2</v>
+      </c>
+      <c r="N73">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D74" s="3">
+        <v>145</v>
+      </c>
+      <c r="E74" s="3">
+        <v>6</v>
+      </c>
+      <c r="F74" s="3">
+        <v>4</v>
+      </c>
+      <c r="G74" s="3">
+        <v>9</v>
+      </c>
+      <c r="H74" s="3">
+        <v>7</v>
+      </c>
+      <c r="I74" s="3">
+        <v>7</v>
+      </c>
+      <c r="J74" s="3">
+        <v>7</v>
+      </c>
+      <c r="K74" s="3">
+        <v>6</v>
+      </c>
+      <c r="L74" s="3">
+        <v>7</v>
+      </c>
+      <c r="M74" s="3">
+        <v>5</v>
+      </c>
+      <c r="N74">
+        <f>SUM(E74:L74)</f>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D75" s="3">
+        <v>164</v>
+      </c>
+      <c r="E75" s="3">
+        <v>8</v>
+      </c>
+      <c r="F75" s="3">
+        <v>1</v>
+      </c>
+      <c r="G75" s="3">
+        <v>4</v>
+      </c>
+      <c r="H75" s="3">
+        <v>9</v>
+      </c>
+      <c r="I75" s="3">
+        <v>8</v>
+      </c>
+      <c r="J75" s="3">
+        <v>15</v>
+      </c>
+      <c r="K75" s="3">
+        <v>6</v>
+      </c>
+      <c r="L75" s="3">
+        <v>3</v>
+      </c>
+      <c r="M75" s="3">
+        <v>4</v>
+      </c>
+      <c r="N75">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D76" s="3">
+        <v>161</v>
+      </c>
+      <c r="E76" s="3">
+        <v>9</v>
+      </c>
+      <c r="F76" s="3">
+        <v>7</v>
+      </c>
+      <c r="G76" s="3">
+        <v>3</v>
+      </c>
+      <c r="H76" s="3">
+        <v>6</v>
+      </c>
+      <c r="I76" s="3">
+        <v>9</v>
+      </c>
+      <c r="J76" s="3">
+        <v>13</v>
+      </c>
+      <c r="K76" s="3">
+        <v>5</v>
+      </c>
+      <c r="L76" s="3">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3">
+        <v>4</v>
+      </c>
+      <c r="N76">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D77" s="3">
+        <v>77</v>
+      </c>
+      <c r="E77" s="3">
+        <v>3</v>
+      </c>
+      <c r="F77" s="3">
+        <v>1</v>
+      </c>
+      <c r="G77" s="3">
+        <v>3</v>
+      </c>
+      <c r="H77" s="3">
+        <v>1</v>
+      </c>
+      <c r="I77" s="3">
+        <v>6</v>
+      </c>
+      <c r="J77" s="3">
+        <v>2</v>
+      </c>
+      <c r="K77" s="3">
+        <v>3</v>
+      </c>
+      <c r="L77" s="3">
+        <v>3</v>
+      </c>
+      <c r="M77" s="3">
+        <v>1</v>
+      </c>
+      <c r="N77">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D78" s="3">
+        <v>152</v>
+      </c>
+      <c r="E78" s="3">
+        <v>2</v>
+      </c>
+      <c r="F78" s="3">
+        <v>4</v>
+      </c>
+      <c r="G78" s="3">
+        <v>4</v>
+      </c>
+      <c r="H78" s="3">
+        <v>2</v>
+      </c>
+      <c r="I78" s="3">
+        <v>3</v>
+      </c>
+      <c r="J78" s="3">
+        <v>3</v>
+      </c>
+      <c r="K78" s="3">
+        <v>4</v>
+      </c>
+      <c r="L78" s="3">
+        <v>3</v>
+      </c>
+      <c r="M78" s="3">
+        <v>1</v>
+      </c>
+      <c r="N78">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D79" s="3">
+        <v>166</v>
+      </c>
+      <c r="E79" s="3">
+        <v>3</v>
+      </c>
+      <c r="F79" s="3">
+        <v>2</v>
+      </c>
+      <c r="G79" s="3">
+        <v>2</v>
+      </c>
+      <c r="H79" s="3">
+        <v>4</v>
+      </c>
+      <c r="I79" s="3">
+        <v>5</v>
+      </c>
+      <c r="J79" s="3">
+        <v>6</v>
+      </c>
+      <c r="K79" s="3">
+        <v>3</v>
+      </c>
+      <c r="L79" s="3">
+        <v>3</v>
+      </c>
+      <c r="M79" s="3">
+        <v>1</v>
+      </c>
+      <c r="N79">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D80" s="3">
+        <v>158</v>
+      </c>
+      <c r="E80" s="3">
+        <v>8</v>
+      </c>
+      <c r="F80" s="3">
+        <v>3</v>
+      </c>
+      <c r="G80" s="3">
+        <v>8</v>
+      </c>
+      <c r="H80" s="3">
+        <v>4</v>
+      </c>
+      <c r="I80" s="3">
+        <v>5</v>
+      </c>
+      <c r="J80" s="3">
+        <v>7</v>
+      </c>
+      <c r="K80" s="3">
+        <v>7</v>
+      </c>
+      <c r="L80" s="3">
+        <v>6</v>
+      </c>
+      <c r="M80" s="3">
+        <v>5</v>
+      </c>
+      <c r="N80">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="81" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D81" s="3">
+        <v>156</v>
+      </c>
+      <c r="E81" s="3">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3">
+        <v>6</v>
+      </c>
+      <c r="G81" s="3">
+        <v>4</v>
+      </c>
+      <c r="H81" s="3">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3">
+        <v>7</v>
+      </c>
+      <c r="J81" s="3">
+        <v>4</v>
+      </c>
+      <c r="K81" s="3">
+        <v>7</v>
+      </c>
+      <c r="L81" s="3">
+        <v>7</v>
+      </c>
+      <c r="M81" s="3">
+        <v>4</v>
+      </c>
+      <c r="N81">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="82" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D82" s="3">
+        <v>161</v>
+      </c>
+      <c r="E82" s="3">
+        <v>18</v>
+      </c>
+      <c r="F82" s="3">
+        <v>13</v>
+      </c>
+      <c r="G82" s="3">
+        <v>32</v>
+      </c>
+      <c r="H82" s="3">
+        <v>14</v>
+      </c>
+      <c r="I82" s="3">
+        <v>30</v>
+      </c>
+      <c r="J82" s="3">
+        <v>31</v>
+      </c>
+      <c r="K82" s="3">
+        <v>7</v>
+      </c>
+      <c r="L82" s="3">
+        <v>16</v>
+      </c>
+      <c r="M82" s="3">
+        <v>30</v>
+      </c>
+      <c r="N82">
+        <f t="shared" si="1"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="83" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D83" s="3">
+        <v>164</v>
+      </c>
+      <c r="E83" s="3">
+        <v>10</v>
+      </c>
+      <c r="F83" s="3">
+        <v>40</v>
+      </c>
+      <c r="G83" s="3">
+        <v>10</v>
+      </c>
+      <c r="H83" s="3">
+        <v>17</v>
+      </c>
+      <c r="I83" s="3">
+        <v>27</v>
+      </c>
+      <c r="J83" s="3">
+        <v>33</v>
+      </c>
+      <c r="K83" s="3">
+        <v>7</v>
+      </c>
+      <c r="L83" s="3">
+        <v>15</v>
+      </c>
+      <c r="M83" s="3">
+        <v>29</v>
+      </c>
+      <c r="N83">
+        <f t="shared" si="1"/>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="84" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D84" s="3">
+        <v>159</v>
+      </c>
+      <c r="E84" s="3">
+        <v>8</v>
+      </c>
+      <c r="F84" s="3">
+        <v>8</v>
+      </c>
+      <c r="G84" s="3">
+        <v>5</v>
+      </c>
+      <c r="H84" s="3">
+        <v>6</v>
+      </c>
+      <c r="I84" s="3">
+        <v>6</v>
+      </c>
+      <c r="J84" s="3">
+        <v>8</v>
+      </c>
+      <c r="K84" s="3">
+        <v>5</v>
+      </c>
+      <c r="L84" s="3">
+        <v>7</v>
+      </c>
+      <c r="M84" s="3">
+        <v>6</v>
+      </c>
+      <c r="N84">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="85" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D85" s="3">
+        <v>158</v>
+      </c>
+      <c r="E85" s="3">
+        <v>9</v>
+      </c>
+      <c r="F85" s="3">
+        <v>7</v>
+      </c>
+      <c r="G85" s="3">
+        <v>7</v>
+      </c>
+      <c r="H85" s="3">
+        <v>6</v>
+      </c>
+      <c r="I85" s="3">
+        <v>5</v>
+      </c>
+      <c r="J85" s="3">
+        <v>7</v>
+      </c>
+      <c r="K85" s="3">
+        <v>4</v>
+      </c>
+      <c r="L85" s="3">
+        <v>7</v>
+      </c>
+      <c r="M85" s="3">
+        <v>6</v>
+      </c>
+      <c r="N85">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="86" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D86" s="3">
+        <v>151</v>
+      </c>
+      <c r="E86" s="3">
+        <v>4</v>
+      </c>
+      <c r="F86" s="3">
+        <v>10</v>
+      </c>
+      <c r="G86" s="3">
+        <v>10</v>
+      </c>
+      <c r="H86" s="3">
+        <v>10</v>
+      </c>
+      <c r="I86" s="3">
+        <v>5</v>
+      </c>
+      <c r="J86" s="3">
+        <v>10</v>
+      </c>
+      <c r="K86" s="3">
+        <v>4</v>
+      </c>
+      <c r="L86" s="3">
+        <v>1</v>
+      </c>
+      <c r="M86" s="3">
+        <v>2</v>
+      </c>
+      <c r="N86">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="87" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B87" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D87" s="3">
+        <v>148</v>
+      </c>
+      <c r="E87" s="3">
+        <v>5</v>
+      </c>
+      <c r="F87" s="3">
+        <v>3</v>
+      </c>
+      <c r="G87" s="3">
+        <v>5</v>
+      </c>
+      <c r="H87" s="3">
+        <v>4</v>
+      </c>
+      <c r="I87" s="3">
+        <v>6</v>
+      </c>
+      <c r="J87" s="3">
+        <v>4</v>
+      </c>
+      <c r="K87" s="3">
+        <v>5</v>
+      </c>
+      <c r="L87" s="3">
+        <v>9</v>
+      </c>
+      <c r="M87" s="3">
+        <v>3</v>
+      </c>
+      <c r="N87">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="88" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D88" s="3">
+        <v>162</v>
+      </c>
+      <c r="E88" s="3">
+        <v>4</v>
+      </c>
+      <c r="F88" s="3">
+        <v>3</v>
+      </c>
+      <c r="G88" s="3">
+        <v>6</v>
+      </c>
+      <c r="H88" s="3">
+        <v>6</v>
+      </c>
+      <c r="I88" s="3">
+        <v>5</v>
+      </c>
+      <c r="J88" s="3">
+        <v>8</v>
+      </c>
+      <c r="K88" s="3">
+        <v>4</v>
+      </c>
+      <c r="L88" s="3">
+        <v>5</v>
+      </c>
+      <c r="M88" s="3">
+        <v>3</v>
+      </c>
+      <c r="N88">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="89" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B89" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D89" s="3">
+        <v>157</v>
+      </c>
+      <c r="E89" s="3">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3">
+        <v>2</v>
+      </c>
+      <c r="G89" s="3">
+        <v>7</v>
+      </c>
+      <c r="H89" s="3">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3">
+        <v>6</v>
+      </c>
+      <c r="K89" s="3">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
+        <v>4</v>
+      </c>
+      <c r="M89" s="3">
+        <v>2</v>
+      </c>
+      <c r="N89">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="90" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B90" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D90" s="3">
+        <v>160</v>
+      </c>
+      <c r="E90" s="3">
+        <v>3</v>
+      </c>
+      <c r="F90" s="3">
+        <v>9</v>
+      </c>
+      <c r="G90" s="3">
+        <v>3</v>
+      </c>
+      <c r="H90" s="3">
+        <v>9</v>
+      </c>
+      <c r="I90" s="3">
+        <v>7</v>
+      </c>
+      <c r="J90" s="3">
+        <v>9</v>
+      </c>
+      <c r="K90" s="3">
+        <v>7</v>
+      </c>
+      <c r="L90" s="3">
+        <v>4</v>
+      </c>
+      <c r="M90" s="3">
+        <v>3</v>
+      </c>
+      <c r="N90">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="91" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D91" s="3">
+        <v>158</v>
+      </c>
+      <c r="E91" s="3">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
+        <v>1</v>
+      </c>
+      <c r="G91" s="3">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3">
+        <v>6</v>
+      </c>
+      <c r="K91" s="3">
+        <v>4</v>
+      </c>
+      <c r="L91" s="3">
+        <v>5</v>
+      </c>
+      <c r="M91" s="3">
+        <v>2</v>
+      </c>
+      <c r="N91">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
     </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D63" s="3">
-        <v>150</v>
-      </c>
-      <c r="E63" s="3">
-        <v>2</v>
-      </c>
-      <c r="F63" s="3">
-        <v>5</v>
-      </c>
-      <c r="G63" s="3">
-        <v>5</v>
-      </c>
-      <c r="H63" s="3">
-        <v>5</v>
-      </c>
-      <c r="I63" s="3">
-        <v>5</v>
-      </c>
-      <c r="J63" s="3">
-        <v>5</v>
-      </c>
-      <c r="K63" s="3">
-        <v>5</v>
-      </c>
-      <c r="L63" s="3">
-        <v>3</v>
-      </c>
-      <c r="M63" s="3">
-        <v>3</v>
-      </c>
-      <c r="N63">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C64" s="3" t="s">
+    <row r="92" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B92" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D64" s="3">
-        <v>125</v>
-      </c>
-      <c r="E64" s="3">
-        <v>2</v>
-      </c>
-      <c r="F64" s="3">
-        <v>2</v>
-      </c>
-      <c r="G64" s="3">
-        <v>3</v>
-      </c>
-      <c r="H64" s="3">
-        <v>1</v>
-      </c>
-      <c r="I64" s="3">
-        <v>3</v>
-      </c>
-      <c r="J64" s="3">
-        <v>3</v>
-      </c>
-      <c r="K64" s="3">
-        <v>3</v>
-      </c>
-      <c r="L64" s="3">
-        <v>3</v>
-      </c>
-      <c r="M64" s="3">
-        <v>3</v>
-      </c>
-      <c r="N64">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D65" s="3">
-        <v>159</v>
-      </c>
-      <c r="E65" s="3">
-        <v>7</v>
-      </c>
-      <c r="F65" s="3">
-        <v>3</v>
-      </c>
-      <c r="G65" s="3">
-        <v>5</v>
-      </c>
-      <c r="H65" s="3">
-        <v>5</v>
-      </c>
-      <c r="I65" s="3">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3">
+      <c r="D92" s="3">
+        <v>163</v>
+      </c>
+      <c r="E92" s="3">
+        <v>3</v>
+      </c>
+      <c r="F92" s="3">
+        <v>4</v>
+      </c>
+      <c r="G92" s="3">
+        <v>4</v>
+      </c>
+      <c r="H92" s="3">
+        <v>10</v>
+      </c>
+      <c r="I92" s="3">
+        <v>8</v>
+      </c>
+      <c r="J92" s="3">
         <v>9</v>
       </c>
-      <c r="K65" s="3">
-        <v>3</v>
-      </c>
-      <c r="L65" s="3">
-        <v>6</v>
-      </c>
-      <c r="M65" s="3">
-        <v>5</v>
-      </c>
-      <c r="N65">
-        <f t="shared" si="1"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D66" s="3">
-        <v>164</v>
-      </c>
-      <c r="E66" s="3">
-        <v>6</v>
-      </c>
-      <c r="F66" s="3">
-        <v>8</v>
-      </c>
-      <c r="G66" s="3">
-        <v>8</v>
-      </c>
-      <c r="H66" s="3">
-        <v>6</v>
-      </c>
-      <c r="I66" s="3">
-        <v>6</v>
-      </c>
-      <c r="J66" s="3">
-        <v>8</v>
-      </c>
-      <c r="K66" s="3">
-        <v>5</v>
-      </c>
-      <c r="L66" s="3">
-        <v>7</v>
-      </c>
-      <c r="M66" s="3">
-        <v>8</v>
-      </c>
-      <c r="N66">
-        <f t="shared" si="1"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D67" s="3">
-        <v>157</v>
-      </c>
-      <c r="E67" s="3">
-        <v>4</v>
-      </c>
-      <c r="F67" s="3">
-        <v>6</v>
-      </c>
-      <c r="G67" s="3">
-        <v>4</v>
-      </c>
-      <c r="H67" s="3">
-        <v>4</v>
-      </c>
-      <c r="I67" s="3">
-        <v>4</v>
-      </c>
-      <c r="J67" s="3">
-        <v>5</v>
-      </c>
-      <c r="K67" s="3">
-        <v>5</v>
-      </c>
-      <c r="L67" s="3">
-        <v>4</v>
-      </c>
-      <c r="M67" s="3">
-        <v>3</v>
-      </c>
-      <c r="N67">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D68" s="3">
-        <v>155</v>
-      </c>
-      <c r="E68" s="3">
-        <v>4</v>
-      </c>
-      <c r="F68" s="3">
-        <v>3</v>
-      </c>
-      <c r="G68" s="3">
-        <v>8</v>
-      </c>
-      <c r="H68" s="3">
-        <v>3</v>
-      </c>
-      <c r="I68" s="3">
-        <v>9</v>
-      </c>
-      <c r="J68" s="3">
-        <v>5</v>
-      </c>
-      <c r="K68" s="3">
-        <v>8</v>
-      </c>
-      <c r="L68" s="3">
-        <v>6</v>
-      </c>
-      <c r="M68" s="3">
-        <v>6</v>
-      </c>
-      <c r="N68">
-        <f t="shared" si="1"/>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D69" s="3">
-        <v>175</v>
-      </c>
-      <c r="E69" s="3">
-        <v>18</v>
-      </c>
-      <c r="F69" s="3">
-        <v>17</v>
-      </c>
-      <c r="G69" s="3">
-        <v>27</v>
-      </c>
-      <c r="H69" s="3">
-        <v>17</v>
-      </c>
-      <c r="I69" s="3">
-        <v>27</v>
-      </c>
-      <c r="J69" s="3">
-        <v>33</v>
-      </c>
-      <c r="K69" s="3">
-        <v>7</v>
-      </c>
-      <c r="L69" s="3">
-        <v>16</v>
-      </c>
-      <c r="M69" s="3">
-        <v>32</v>
-      </c>
-      <c r="N69">
-        <f t="shared" si="1"/>
-        <v>162</v>
-      </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D70" s="3">
-        <v>155</v>
-      </c>
-      <c r="E70" s="3">
-        <v>22</v>
-      </c>
-      <c r="F70" s="3">
-        <v>20</v>
-      </c>
-      <c r="G70" s="3">
-        <v>29</v>
-      </c>
-      <c r="H70" s="3">
-        <v>18</v>
-      </c>
-      <c r="I70" s="3">
-        <v>29</v>
-      </c>
-      <c r="J70" s="3">
-        <v>32</v>
-      </c>
-      <c r="K70" s="3">
-        <v>7</v>
-      </c>
-      <c r="L70" s="3">
-        <v>15</v>
-      </c>
-      <c r="M70" s="3">
-        <v>32</v>
-      </c>
-      <c r="N70">
-        <f t="shared" si="1"/>
-        <v>172</v>
-      </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D71" s="3">
-        <v>158</v>
-      </c>
-      <c r="E71" s="3">
-        <v>8</v>
-      </c>
-      <c r="F71" s="3">
-        <v>3</v>
-      </c>
-      <c r="G71" s="3">
-        <v>3</v>
-      </c>
-      <c r="H71" s="3">
-        <v>6</v>
-      </c>
-      <c r="I71" s="3">
-        <v>7</v>
-      </c>
-      <c r="J71" s="3">
-        <v>8</v>
-      </c>
-      <c r="K71" s="3">
-        <v>5</v>
-      </c>
-      <c r="L71" s="3">
-        <v>3</v>
-      </c>
-      <c r="M71" s="3">
-        <v>3</v>
-      </c>
-      <c r="N71">
-        <f t="shared" si="1"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D72" s="3">
-        <v>145</v>
-      </c>
-      <c r="E72" s="3">
-        <v>7</v>
-      </c>
-      <c r="F72" s="3">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3">
-        <v>9</v>
-      </c>
-      <c r="H72" s="3">
-        <v>7</v>
-      </c>
-      <c r="I72" s="3">
-        <v>8</v>
-      </c>
-      <c r="J72" s="3">
-        <v>8</v>
-      </c>
-      <c r="K72" s="3">
-        <v>6</v>
-      </c>
-      <c r="L72" s="3">
-        <v>7</v>
-      </c>
-      <c r="M72" s="3">
-        <v>6</v>
-      </c>
-      <c r="N72">
-        <f t="shared" si="1"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D73" s="3">
-        <v>164</v>
-      </c>
-      <c r="E73" s="3">
-        <v>8</v>
-      </c>
-      <c r="F73" s="3">
-        <v>1</v>
-      </c>
-      <c r="G73" s="3">
-        <v>4</v>
-      </c>
-      <c r="H73" s="3">
-        <v>9</v>
-      </c>
-      <c r="I73" s="3">
-        <v>8</v>
-      </c>
-      <c r="J73" s="3">
-        <v>15</v>
-      </c>
-      <c r="K73" s="3">
-        <v>6</v>
-      </c>
-      <c r="L73" s="3">
-        <v>3</v>
-      </c>
-      <c r="M73" s="3">
-        <v>4</v>
-      </c>
-      <c r="N73">
-        <f t="shared" si="1"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D74" s="3">
-        <v>161</v>
-      </c>
-      <c r="E74" s="3">
-        <v>9</v>
-      </c>
-      <c r="F74" s="3">
-        <v>7</v>
-      </c>
-      <c r="G74" s="3">
-        <v>3</v>
-      </c>
-      <c r="H74" s="3">
-        <v>6</v>
-      </c>
-      <c r="I74" s="3">
-        <v>9</v>
-      </c>
-      <c r="J74" s="3">
-        <v>13</v>
-      </c>
-      <c r="K74" s="3">
-        <v>5</v>
-      </c>
-      <c r="L74" s="3">
-        <v>3</v>
-      </c>
-      <c r="M74" s="3">
-        <v>4</v>
-      </c>
-      <c r="N74">
-        <f t="shared" si="1"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D75" s="3">
-        <v>77</v>
-      </c>
-      <c r="E75" s="3">
-        <v>3</v>
-      </c>
-      <c r="F75" s="3">
-        <v>1</v>
-      </c>
-      <c r="G75" s="3">
-        <v>3</v>
-      </c>
-      <c r="H75" s="3">
-        <v>1</v>
-      </c>
-      <c r="I75" s="3">
-        <v>6</v>
-      </c>
-      <c r="J75" s="3">
-        <v>2</v>
-      </c>
-      <c r="K75" s="3">
-        <v>3</v>
-      </c>
-      <c r="L75" s="3">
-        <v>3</v>
-      </c>
-      <c r="M75" s="3">
-        <v>1</v>
-      </c>
-      <c r="N75">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D76" s="3">
-        <v>152</v>
-      </c>
-      <c r="E76" s="3">
-        <v>2</v>
-      </c>
-      <c r="F76" s="3">
-        <v>4</v>
-      </c>
-      <c r="G76" s="3">
-        <v>4</v>
-      </c>
-      <c r="H76" s="3">
-        <v>2</v>
-      </c>
-      <c r="I76" s="3">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3">
-        <v>4</v>
-      </c>
-      <c r="L76" s="3">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3">
-        <v>1</v>
-      </c>
-      <c r="N76">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D77" s="3">
-        <v>166</v>
-      </c>
-      <c r="E77" s="3">
-        <v>3</v>
-      </c>
-      <c r="F77" s="3">
-        <v>2</v>
-      </c>
-      <c r="G77" s="3">
-        <v>2</v>
-      </c>
-      <c r="H77" s="3">
-        <v>4</v>
-      </c>
-      <c r="I77" s="3">
-        <v>5</v>
-      </c>
-      <c r="J77" s="3">
-        <v>6</v>
-      </c>
-      <c r="K77" s="3">
-        <v>3</v>
-      </c>
-      <c r="L77" s="3">
-        <v>3</v>
-      </c>
-      <c r="M77" s="3">
-        <v>1</v>
-      </c>
-      <c r="N77">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="78" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D78" s="3">
-        <v>158</v>
-      </c>
-      <c r="E78" s="3">
-        <v>8</v>
-      </c>
-      <c r="F78" s="3">
-        <v>3</v>
-      </c>
-      <c r="G78" s="3">
-        <v>8</v>
-      </c>
-      <c r="H78" s="3">
-        <v>4</v>
-      </c>
-      <c r="I78" s="3">
-        <v>5</v>
-      </c>
-      <c r="J78" s="3">
-        <v>7</v>
-      </c>
-      <c r="K78" s="3">
-        <v>7</v>
-      </c>
-      <c r="L78" s="3">
-        <v>6</v>
-      </c>
-      <c r="M78" s="3">
-        <v>6</v>
-      </c>
-      <c r="N78">
-        <f t="shared" si="1"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D79" s="3">
-        <v>156</v>
-      </c>
-      <c r="E79" s="3">
-        <v>3</v>
-      </c>
-      <c r="F79" s="3">
-        <v>6</v>
-      </c>
-      <c r="G79" s="3">
-        <v>4</v>
-      </c>
-      <c r="H79" s="3">
-        <v>3</v>
-      </c>
-      <c r="I79" s="3">
-        <v>7</v>
-      </c>
-      <c r="J79" s="3">
-        <v>4</v>
-      </c>
-      <c r="K79" s="3">
-        <v>7</v>
-      </c>
-      <c r="L79" s="3">
-        <v>7</v>
-      </c>
-      <c r="M79" s="3">
-        <v>5</v>
-      </c>
-      <c r="N79">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D80" s="3">
-        <v>161</v>
-      </c>
-      <c r="E80" s="3">
-        <v>18</v>
-      </c>
-      <c r="F80" s="3">
-        <v>13</v>
-      </c>
-      <c r="G80" s="3">
-        <v>32</v>
-      </c>
-      <c r="H80" s="3">
-        <v>14</v>
-      </c>
-      <c r="I80" s="3">
-        <v>30</v>
-      </c>
-      <c r="J80" s="3">
-        <v>31</v>
-      </c>
-      <c r="K80" s="3">
-        <v>7</v>
-      </c>
-      <c r="L80" s="3">
-        <v>16</v>
-      </c>
-      <c r="M80" s="3">
-        <v>30</v>
-      </c>
-      <c r="N80">
-        <f t="shared" si="1"/>
-        <v>161</v>
-      </c>
-    </row>
-    <row r="81" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D81" s="3">
-        <v>164</v>
-      </c>
-      <c r="E81" s="3">
-        <v>10</v>
-      </c>
-      <c r="F81" s="3">
-        <v>40</v>
-      </c>
-      <c r="G81" s="3">
-        <v>10</v>
-      </c>
-      <c r="H81" s="3">
-        <v>17</v>
-      </c>
-      <c r="I81" s="3">
-        <v>27</v>
-      </c>
-      <c r="J81" s="3">
-        <v>33</v>
-      </c>
-      <c r="K81" s="3">
-        <v>7</v>
-      </c>
-      <c r="L81" s="3">
-        <v>15</v>
-      </c>
-      <c r="M81" s="3">
-        <v>29</v>
-      </c>
-      <c r="N81">
-        <f t="shared" si="1"/>
-        <v>159</v>
-      </c>
-    </row>
-    <row r="82" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D82" s="3">
-        <v>159</v>
-      </c>
-      <c r="E82" s="3">
-        <v>8</v>
-      </c>
-      <c r="F82" s="3">
-        <v>8</v>
-      </c>
-      <c r="G82" s="3">
-        <v>5</v>
-      </c>
-      <c r="H82" s="3">
-        <v>6</v>
-      </c>
-      <c r="I82" s="3">
-        <v>6</v>
-      </c>
-      <c r="J82" s="3">
-        <v>8</v>
-      </c>
-      <c r="K82" s="3">
-        <v>5</v>
-      </c>
-      <c r="L82" s="3">
-        <v>7</v>
-      </c>
-      <c r="M82" s="3">
-        <v>7</v>
-      </c>
-      <c r="N82">
-        <f t="shared" si="1"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="83" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D83" s="3">
-        <v>158</v>
-      </c>
-      <c r="E83" s="3">
-        <v>9</v>
-      </c>
-      <c r="F83" s="3">
-        <v>7</v>
-      </c>
-      <c r="G83" s="3">
-        <v>7</v>
-      </c>
-      <c r="H83" s="3">
-        <v>6</v>
-      </c>
-      <c r="I83" s="3">
-        <v>5</v>
-      </c>
-      <c r="J83" s="3">
-        <v>7</v>
-      </c>
-      <c r="K83" s="3">
-        <v>4</v>
-      </c>
-      <c r="L83" s="3">
-        <v>7</v>
-      </c>
-      <c r="M83" s="3">
-        <v>7</v>
-      </c>
-      <c r="N83">
-        <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="84" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D84" s="3">
-        <v>151</v>
-      </c>
-      <c r="E84" s="3">
-        <v>4</v>
-      </c>
-      <c r="F84" s="3">
-        <v>10</v>
-      </c>
-      <c r="G84" s="3">
-        <v>10</v>
-      </c>
-      <c r="H84" s="3">
-        <v>10</v>
-      </c>
-      <c r="I84" s="3">
-        <v>2</v>
-      </c>
-      <c r="J84" s="3">
-        <v>10</v>
-      </c>
-      <c r="K84" s="3">
-        <v>4</v>
-      </c>
-      <c r="L84" s="3">
-        <v>1</v>
-      </c>
-      <c r="M84" s="3">
-        <v>2</v>
-      </c>
-      <c r="N84">
+      <c r="K92" s="3">
+        <v>6</v>
+      </c>
+      <c r="L92" s="3">
+        <v>7</v>
+      </c>
+      <c r="M92" s="3">
+        <v>7</v>
+      </c>
+      <c r="N92">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
     </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D85" s="3">
-        <v>148</v>
-      </c>
-      <c r="E85" s="3">
-        <v>5</v>
-      </c>
-      <c r="F85" s="3">
-        <v>3</v>
-      </c>
-      <c r="G85" s="3">
-        <v>5</v>
-      </c>
-      <c r="H85" s="3">
-        <v>4</v>
-      </c>
-      <c r="I85" s="3">
-        <v>6</v>
-      </c>
-      <c r="J85" s="3">
-        <v>4</v>
-      </c>
-      <c r="K85" s="3">
-        <v>5</v>
-      </c>
-      <c r="L85" s="3">
-        <v>9</v>
-      </c>
-      <c r="M85" s="3">
-        <v>4</v>
-      </c>
-      <c r="N85">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="86" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D86" s="3">
-        <v>162</v>
-      </c>
-      <c r="E86" s="3">
-        <v>4</v>
-      </c>
-      <c r="F86" s="3">
-        <v>3</v>
-      </c>
-      <c r="G86" s="3">
-        <v>6</v>
-      </c>
-      <c r="H86" s="3">
-        <v>6</v>
-      </c>
-      <c r="I86" s="3">
-        <v>5</v>
-      </c>
-      <c r="J86" s="3">
-        <v>8</v>
-      </c>
-      <c r="K86" s="3">
-        <v>4</v>
-      </c>
-      <c r="L86" s="3">
-        <v>5</v>
-      </c>
-      <c r="M86" s="3">
-        <v>4</v>
-      </c>
-      <c r="N86">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="87" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D87" s="3">
-        <v>157</v>
-      </c>
-      <c r="E87" s="3">
-        <v>5</v>
-      </c>
-      <c r="F87" s="3">
-        <v>2</v>
-      </c>
-      <c r="G87" s="3">
-        <v>7</v>
-      </c>
-      <c r="H87" s="3">
-        <v>5</v>
-      </c>
-      <c r="I87" s="3">
-        <v>5</v>
-      </c>
-      <c r="J87" s="3">
-        <v>6</v>
-      </c>
-      <c r="K87" s="3">
-        <v>5</v>
-      </c>
-      <c r="L87" s="3">
-        <v>4</v>
-      </c>
-      <c r="M87" s="3">
-        <v>3</v>
-      </c>
-      <c r="N87">
-        <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="88" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D88" s="3">
-        <v>160</v>
-      </c>
-      <c r="E88" s="3">
-        <v>3</v>
-      </c>
-      <c r="F88" s="3">
-        <v>9</v>
-      </c>
-      <c r="G88" s="3">
-        <v>3</v>
-      </c>
-      <c r="H88" s="3">
-        <v>9</v>
-      </c>
-      <c r="I88" s="3">
-        <v>7</v>
-      </c>
-      <c r="J88" s="3">
-        <v>9</v>
-      </c>
-      <c r="K88" s="3">
-        <v>7</v>
-      </c>
-      <c r="L88" s="3">
-        <v>4</v>
-      </c>
-      <c r="M88" s="3">
-        <v>3</v>
-      </c>
-      <c r="N88">
-        <f t="shared" si="1"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="89" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D89" s="3">
-        <v>158</v>
-      </c>
-      <c r="E89" s="3">
-        <v>3</v>
-      </c>
-      <c r="F89" s="3">
+    <row r="93" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B93" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="94" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B94" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G89" s="3">
-        <v>8</v>
-      </c>
-      <c r="H89" s="3">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3">
-        <v>6</v>
-      </c>
-      <c r="K89" s="3">
-        <v>4</v>
-      </c>
-      <c r="L89" s="3">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
-        <v>3</v>
-      </c>
-      <c r="N89">
-        <f t="shared" si="1"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="90" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B90" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="91" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B91" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J91" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K91" s="2"/>
-    </row>
-    <row r="92" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" t="s">
-        <v>70</v>
-      </c>
-      <c r="C92" t="s">
-        <v>66</v>
-      </c>
-      <c r="D92">
-        <v>6</v>
-      </c>
-      <c r="E92">
-        <v>2</v>
-      </c>
-      <c r="F92">
-        <v>3</v>
-      </c>
-      <c r="I92">
-        <v>8</v>
-      </c>
-      <c r="J92">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="93" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B93" t="s">
-        <v>67</v>
-      </c>
-      <c r="C93" t="s">
-        <v>66</v>
-      </c>
-      <c r="D93">
-        <v>5</v>
-      </c>
-      <c r="E93">
-        <v>7</v>
-      </c>
-      <c r="F93">
-        <v>6</v>
-      </c>
-      <c r="I93">
-        <v>8</v>
-      </c>
-      <c r="J93">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="94" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B94" t="s">
-        <v>68</v>
-      </c>
-      <c r="C94" t="s">
-        <v>66</v>
-      </c>
-      <c r="D94">
-        <v>15</v>
-      </c>
-      <c r="E94">
-        <v>12</v>
-      </c>
-      <c r="F94">
-        <v>5</v>
-      </c>
-      <c r="I94">
-        <v>13</v>
-      </c>
-      <c r="J94">
-        <v>27</v>
-      </c>
+      <c r="C94" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="2"/>
     </row>
     <row r="95" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C95" t="s">
         <v>66</v>
       </c>
       <c r="D95">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E95">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F95">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I95">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J95">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C96" t="s">
         <v>66</v>
       </c>
       <c r="D96">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E96">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F96">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I96">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J96">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C97" t="s">
         <v>66</v>
       </c>
       <c r="D97">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E97">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F97">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I97">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J97">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C98" t="s">
         <v>66</v>
       </c>
       <c r="D98">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E98">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F98">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I98">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J98">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="C99" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D99">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E99">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F99">
         <v>3</v>
       </c>
       <c r="I99">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J99">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="C100" t="s">
         <v>66</v>
       </c>
       <c r="D100">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F100">
         <v>3</v>
       </c>
       <c r="I100">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B101" t="s">
+        <v>77</v>
+      </c>
+      <c r="C101" t="s">
+        <v>66</v>
+      </c>
+      <c r="D101">
+        <v>17</v>
+      </c>
+      <c r="E101">
+        <v>14</v>
+      </c>
+      <c r="F101">
+        <v>5</v>
+      </c>
+      <c r="I101">
+        <v>15</v>
+      </c>
+      <c r="J101">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B102" t="s">
+        <v>83</v>
+      </c>
+      <c r="C102" t="s">
+        <v>84</v>
+      </c>
+      <c r="D102">
+        <v>6</v>
+      </c>
+      <c r="E102">
+        <v>3</v>
+      </c>
+      <c r="F102">
+        <v>3</v>
+      </c>
+      <c r="I102">
+        <v>6</v>
+      </c>
+      <c r="J102">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B103" t="s">
+        <v>106</v>
+      </c>
+      <c r="C103" t="s">
+        <v>66</v>
+      </c>
+      <c r="D103">
+        <v>3</v>
+      </c>
+      <c r="E103">
+        <v>3</v>
+      </c>
+      <c r="F103">
+        <v>3</v>
+      </c>
+      <c r="I103">
+        <v>5</v>
+      </c>
+      <c r="J103">
         <v>2</v>
       </c>
     </row>
